--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE3CBAF-EF33-4BB2-9E93-78D760FB8031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9A4681-50B8-4BE3-AEED-887107FFAE72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1215" windowWidth="20505" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="440">
   <si>
     <t>KRZ502593210</t>
   </si>
@@ -1313,6 +1313,210 @@
   </si>
   <si>
     <t>쿼드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Team</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글로벌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식(메자닌)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502668310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥국5호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502665150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대인베SB15호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502659840</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대인베SB14호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20262-02-06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502660730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화139호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화137호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502658630</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502661290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나31호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권형(외화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502657400	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나29호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">KRZ502653000	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나28호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502665633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오라이언135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502661860</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신한달러인컴10호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신한Credit4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502668450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502662461</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브이아이52호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502665980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이프메자닌4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502662310	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신2602호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	KRZ502663590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신SB2602호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502660710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신SB2601호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502661570</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NH아문디S22호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502660560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NH아문디S21호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502668340</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NH아문디57호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502664810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBK5호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRZ502660670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDC3호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권(원화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권(외화)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1356,17 +1560,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1380,16 +1591,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5A487DC3-37D8-45C7-A233-D56F8654573A}" name="표2" displayName="표2" ref="A1:D164" totalsRowShown="0">
-  <autoFilter ref="A1:D164" xr:uid="{5A487DC3-37D8-45C7-A233-D56F8654573A}"/>
-  <sortState ref="A2:D164">
-    <sortCondition descending="1" ref="C2"/>
-  </sortState>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5A487DC3-37D8-45C7-A233-D56F8654573A}" name="표2" displayName="표2" ref="A1:F185" totalsRowShown="0">
+  <autoFilter ref="A1:F185" xr:uid="{5A487DC3-37D8-45C7-A233-D56F8654573A}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{D40BE4DD-43FE-49E9-8436-592CF8FBE35A}" name="Code"/>
     <tableColumn id="2" xr3:uid="{F336053D-BD49-47F3-B249-5103E50F80C9}" name="Fund"/>
     <tableColumn id="3" xr3:uid="{E1C8362A-7D25-46CB-84F2-B24CBD02573D}" name="Group"/>
     <tableColumn id="4" xr3:uid="{BA29F747-744C-4972-9F74-DA724AD556E2}" name="Manager"/>
+    <tableColumn id="5" xr3:uid="{C22D9EDE-63FD-432F-8D76-ACB553928B79}" name="LaunchDate"/>
+    <tableColumn id="6" xr3:uid="{6C0805FC-F20A-4557-BD3F-24A9694B7E2C}" name="Team" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1717,16 +1927,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>135</v>
       </c>
@@ -1742,8 +1953,11 @@
       <c r="E1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1756,8 +1970,11 @@
       <c r="D2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1770,8 +1987,11 @@
       <c r="D3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1784,8 +2004,11 @@
       <c r="D4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1798,8 +2021,11 @@
       <c r="D5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>183</v>
       </c>
@@ -1812,8 +2038,11 @@
       <c r="D6" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>184</v>
       </c>
@@ -1826,8 +2055,11 @@
       <c r="D7" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -1840,153 +2072,198 @@
       <c r="D8" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C9" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46078</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>407</v>
+      </c>
+      <c r="B10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="1">
+        <v>46043</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46008</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>186</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" t="s">
         <v>270</v>
       </c>
-      <c r="C9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D12" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="F12" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>187</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C13" t="s">
+        <v>265</v>
+      </c>
+      <c r="D13" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="F13" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>188</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>272</v>
       </c>
-      <c r="C11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="F14" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>189</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>273</v>
       </c>
-      <c r="C12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="F15" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>190</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>274</v>
       </c>
-      <c r="C13" t="s">
-        <v>265</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="F16" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>417</v>
+      </c>
+      <c r="B17" t="s">
+        <v>418</v>
+      </c>
+      <c r="C17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46080</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>191</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B18" t="s">
         <v>276</v>
       </c>
-      <c r="C14" t="s">
-        <v>265</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C18" t="s">
+        <v>265</v>
+      </c>
+      <c r="D18" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>278</v>
-      </c>
-      <c r="C15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D15" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D16" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>194</v>
-      </c>
-      <c r="B17" t="s">
-        <v>280</v>
-      </c>
-      <c r="C17" t="s">
-        <v>265</v>
-      </c>
-      <c r="D17" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C18" t="s">
-        <v>265</v>
-      </c>
-      <c r="D18" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F18" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>431</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>432</v>
       </c>
       <c r="C19" t="s">
         <v>265</v>
@@ -1994,335 +2271,410 @@
       <c r="D19" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="1">
+        <v>46128</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" t="s">
+        <v>279</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D22" t="s">
+        <v>281</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" t="s">
+        <v>281</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>197</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B25" t="s">
         <v>284</v>
       </c>
-      <c r="C20" t="s">
-        <v>265</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="F25" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>198</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B26" t="s">
         <v>285</v>
       </c>
-      <c r="C21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C26" t="s">
+        <v>265</v>
+      </c>
+      <c r="D26" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="F26" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>199</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B27" t="s">
         <v>286</v>
       </c>
-      <c r="C22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C27" t="s">
+        <v>265</v>
+      </c>
+      <c r="D27" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="F27" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>200</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B28" t="s">
         <v>287</v>
       </c>
-      <c r="C23" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C28" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="F28" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>201</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B29" t="s">
         <v>289</v>
       </c>
-      <c r="C24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C29" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="F29" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>202</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B30" t="s">
         <v>291</v>
       </c>
-      <c r="C25" t="s">
-        <v>265</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C30" t="s">
+        <v>265</v>
+      </c>
+      <c r="D30" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="F30" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>203</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B31" t="s">
         <v>293</v>
       </c>
-      <c r="C26" t="s">
-        <v>265</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C31" t="s">
+        <v>265</v>
+      </c>
+      <c r="D31" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="F31" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>204</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B32" t="s">
         <v>294</v>
       </c>
-      <c r="C27" t="s">
-        <v>265</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D32" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="F32" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>205</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B33" t="s">
         <v>295</v>
       </c>
-      <c r="C28" t="s">
-        <v>265</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D33" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="F33" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>206</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B34" t="s">
         <v>297</v>
       </c>
-      <c r="C29" t="s">
-        <v>265</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="F34" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>207</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B35" t="s">
         <v>299</v>
       </c>
-      <c r="C30" t="s">
-        <v>265</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C35" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="F35" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>208</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B36" t="s">
         <v>300</v>
       </c>
-      <c r="C31" t="s">
-        <v>265</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C36" t="s">
+        <v>265</v>
+      </c>
+      <c r="D36" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="F36" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>209</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B37" t="s">
         <v>301</v>
       </c>
-      <c r="C32" t="s">
-        <v>265</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C37" t="s">
+        <v>265</v>
+      </c>
+      <c r="D37" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="F37" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>210</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B38" t="s">
         <v>302</v>
       </c>
-      <c r="C33" t="s">
-        <v>265</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C38" t="s">
+        <v>265</v>
+      </c>
+      <c r="D38" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="F38" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>211</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B39" t="s">
         <v>303</v>
       </c>
-      <c r="C34" t="s">
-        <v>265</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C39" t="s">
+        <v>265</v>
+      </c>
+      <c r="D39" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="F39" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>212</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B40" t="s">
         <v>304</v>
       </c>
-      <c r="C35" t="s">
-        <v>265</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D40" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="F40" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>213</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B41" t="s">
         <v>306</v>
       </c>
-      <c r="C36" t="s">
-        <v>265</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C41" t="s">
+        <v>265</v>
+      </c>
+      <c r="D41" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="F41" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>214</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B42" t="s">
         <v>307</v>
       </c>
-      <c r="C37" t="s">
-        <v>265</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C42" t="s">
+        <v>265</v>
+      </c>
+      <c r="D42" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="F42" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>215</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B43" t="s">
         <v>309</v>
-      </c>
-      <c r="C38" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>216</v>
-      </c>
-      <c r="B39" t="s">
-        <v>310</v>
-      </c>
-      <c r="C39" t="s">
-        <v>265</v>
-      </c>
-      <c r="D39" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>232</v>
-      </c>
-      <c r="B40" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" t="s">
-        <v>265</v>
-      </c>
-      <c r="D40" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>234</v>
-      </c>
-      <c r="B41" t="s">
-        <v>312</v>
-      </c>
-      <c r="C41" t="s">
-        <v>265</v>
-      </c>
-      <c r="D41" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>238</v>
-      </c>
-      <c r="B42" t="s">
-        <v>314</v>
-      </c>
-      <c r="C42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D42" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>240</v>
-      </c>
-      <c r="B43" t="s">
-        <v>315</v>
       </c>
       <c r="C43" t="s">
         <v>265</v>
@@ -2330,335 +2682,419 @@
       <c r="D43" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F43" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" t="s">
+        <v>310</v>
+      </c>
+      <c r="C44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" t="s">
+        <v>290</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>232</v>
+      </c>
+      <c r="B45" t="s">
+        <v>311</v>
+      </c>
+      <c r="C45" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C46" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" t="s">
+        <v>313</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>393</v>
+      </c>
+      <c r="B47" t="s">
+        <v>394</v>
+      </c>
+      <c r="C47" t="s">
+        <v>265</v>
+      </c>
+      <c r="D47" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" s="1">
+        <v>46128</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" t="s">
+        <v>265</v>
+      </c>
+      <c r="D48" t="s">
+        <v>268</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>240</v>
+      </c>
+      <c r="B49" t="s">
+        <v>315</v>
+      </c>
+      <c r="C49" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" t="s">
+        <v>268</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>242</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B50" t="s">
         <v>316</v>
       </c>
-      <c r="C44" t="s">
-        <v>265</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C50" t="s">
+        <v>265</v>
+      </c>
+      <c r="D50" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="F50" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>245</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B51" t="s">
         <v>318</v>
       </c>
-      <c r="C45" t="s">
-        <v>265</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C51" t="s">
+        <v>265</v>
+      </c>
+      <c r="D51" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="F51" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>247</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B52" t="s">
         <v>320</v>
       </c>
-      <c r="C46" t="s">
-        <v>265</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C52" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="F52" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>248</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B53" t="s">
         <v>321</v>
       </c>
-      <c r="C47" t="s">
-        <v>265</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C53" t="s">
+        <v>265</v>
+      </c>
+      <c r="D53" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="F53" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>253</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>323</v>
       </c>
-      <c r="C48" t="s">
-        <v>265</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="F54" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>254</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B55" t="s">
         <v>324</v>
       </c>
-      <c r="C49" t="s">
-        <v>265</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C55" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="F55" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>256</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B56" t="s">
         <v>325</v>
       </c>
-      <c r="C50" t="s">
-        <v>265</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C56" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="F56" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>257</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B57" t="s">
         <v>326</v>
       </c>
-      <c r="C51" t="s">
-        <v>265</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C57" t="s">
+        <v>265</v>
+      </c>
+      <c r="D57" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="F57" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>258</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B58" t="s">
         <v>327</v>
       </c>
-      <c r="C52" t="s">
-        <v>265</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C58" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="F58" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>433</v>
+      </c>
+      <c r="B59" t="s">
+        <v>434</v>
+      </c>
+      <c r="C59" t="s">
+        <v>406</v>
+      </c>
+      <c r="D59" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="1">
+        <v>46100</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>435</v>
+      </c>
+      <c r="B60" t="s">
+        <v>436</v>
+      </c>
+      <c r="C60" t="s">
+        <v>406</v>
+      </c>
+      <c r="D60" t="s">
+        <v>437</v>
+      </c>
+      <c r="E60" s="1">
+        <v>46064</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>260</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B61" t="s">
         <v>329</v>
       </c>
-      <c r="C53" t="s">
-        <v>265</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C61" t="s">
+        <v>265</v>
+      </c>
+      <c r="D61" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="F61" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>262</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B62" t="s">
         <v>330</v>
       </c>
-      <c r="C54" t="s">
-        <v>265</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C62" t="s">
+        <v>265</v>
+      </c>
+      <c r="D62" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="F62" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>263</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B63" t="s">
         <v>331</v>
       </c>
-      <c r="C55" t="s">
-        <v>265</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D63" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="F63" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>421</v>
+      </c>
+      <c r="B64" t="s">
+        <v>422</v>
+      </c>
+      <c r="C64" t="s">
+        <v>265</v>
+      </c>
+      <c r="D64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E64" s="1">
+        <v>46079</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>220</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B65" t="s">
         <v>332</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C65" t="s">
         <v>333</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D65" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="F65" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>217</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B66" t="s">
         <v>334</v>
-      </c>
-      <c r="C57" t="s">
-        <v>335</v>
-      </c>
-      <c r="D57" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>218</v>
-      </c>
-      <c r="B58" t="s">
-        <v>336</v>
-      </c>
-      <c r="C58" t="s">
-        <v>335</v>
-      </c>
-      <c r="D58" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" t="s">
-        <v>337</v>
-      </c>
-      <c r="C59" t="s">
-        <v>335</v>
-      </c>
-      <c r="D59" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>221</v>
-      </c>
-      <c r="B60" t="s">
-        <v>338</v>
-      </c>
-      <c r="C60" t="s">
-        <v>335</v>
-      </c>
-      <c r="D60" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61" t="s">
-        <v>339</v>
-      </c>
-      <c r="C61" t="s">
-        <v>335</v>
-      </c>
-      <c r="D61" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>223</v>
-      </c>
-      <c r="B62" t="s">
-        <v>340</v>
-      </c>
-      <c r="C62" t="s">
-        <v>335</v>
-      </c>
-      <c r="D62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>224</v>
-      </c>
-      <c r="B63" t="s">
-        <v>341</v>
-      </c>
-      <c r="C63" t="s">
-        <v>335</v>
-      </c>
-      <c r="D63" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>225</v>
-      </c>
-      <c r="B64" t="s">
-        <v>342</v>
-      </c>
-      <c r="C64" t="s">
-        <v>335</v>
-      </c>
-      <c r="D64" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" t="s">
-        <v>343</v>
-      </c>
-      <c r="C65" t="s">
-        <v>335</v>
-      </c>
-      <c r="D65" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>227</v>
-      </c>
-      <c r="B66" t="s">
-        <v>344</v>
       </c>
       <c r="C66" t="s">
         <v>335</v>
       </c>
       <c r="D66" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
         <v>335</v>
@@ -2666,131 +3102,161 @@
       <c r="D67" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B68" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C68" t="s">
         <v>335</v>
       </c>
       <c r="D68" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C69" t="s">
         <v>335</v>
       </c>
       <c r="D69" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B70" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C70" t="s">
         <v>335</v>
       </c>
       <c r="D70" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s">
-        <v>349</v>
+        <v>424</v>
       </c>
       <c r="C71" t="s">
         <v>335</v>
       </c>
       <c r="D71" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+      <c r="E71" s="1">
+        <v>46140</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s">
-        <v>350</v>
+        <v>426</v>
       </c>
       <c r="C72" t="s">
         <v>335</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+      <c r="E72" s="1">
+        <v>46072</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B73" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="C73" t="s">
         <v>335</v>
       </c>
       <c r="D73" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>413</v>
       </c>
       <c r="B74" t="s">
-        <v>352</v>
+        <v>414</v>
       </c>
       <c r="C74" t="s">
         <v>335</v>
       </c>
       <c r="D74" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="E74" s="1">
-        <v>45659</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46078</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C75" t="s">
         <v>335</v>
       </c>
       <c r="D75" t="s">
-        <v>288</v>
-      </c>
-      <c r="E75" s="1">
-        <v>45693</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C76" t="s">
         <v>335</v>
@@ -2798,16 +3264,16 @@
       <c r="D76" t="s">
         <v>292</v>
       </c>
-      <c r="E76" s="1">
-        <v>45659</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B77" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C77" t="s">
         <v>335</v>
@@ -2815,1201 +3281,1843 @@
       <c r="D77" t="s">
         <v>288</v>
       </c>
-      <c r="E77" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C78" t="s">
         <v>335</v>
       </c>
       <c r="D78" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="B79" t="s">
-        <v>357</v>
+        <v>428</v>
       </c>
       <c r="C79" t="s">
         <v>335</v>
       </c>
       <c r="D79" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="E79" s="1">
+        <v>46078</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>429</v>
       </c>
       <c r="B80" t="s">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
         <v>335</v>
       </c>
       <c r="D80" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="E80" s="1">
+        <v>46072</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="B81" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="C81" t="s">
         <v>335</v>
       </c>
       <c r="D81" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B82" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="C82" t="s">
         <v>335</v>
       </c>
       <c r="D82" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B83" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C83" t="s">
         <v>335</v>
       </c>
       <c r="D83" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="B84" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C84" t="s">
         <v>335</v>
       </c>
       <c r="D84" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B85" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C85" t="s">
         <v>335</v>
       </c>
       <c r="D85" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="C86" t="s">
         <v>335</v>
       </c>
       <c r="D86" t="s">
+        <v>328</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>236</v>
+      </c>
+      <c r="B87" t="s">
+        <v>351</v>
+      </c>
+      <c r="C87" t="s">
+        <v>335</v>
+      </c>
+      <c r="D87" t="s">
+        <v>275</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>237</v>
+      </c>
+      <c r="B88" t="s">
+        <v>352</v>
+      </c>
+      <c r="C88" t="s">
+        <v>335</v>
+      </c>
+      <c r="D88" t="s">
+        <v>277</v>
+      </c>
+      <c r="E88" s="1">
+        <v>45659</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>239</v>
+      </c>
+      <c r="B89" t="s">
+        <v>353</v>
+      </c>
+      <c r="C89" t="s">
+        <v>335</v>
+      </c>
+      <c r="D89" t="s">
+        <v>288</v>
+      </c>
+      <c r="E89" s="1">
+        <v>45693</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" t="s">
+        <v>354</v>
+      </c>
+      <c r="C90" t="s">
+        <v>335</v>
+      </c>
+      <c r="D90" t="s">
+        <v>292</v>
+      </c>
+      <c r="E90" s="1">
+        <v>45659</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>243</v>
+      </c>
+      <c r="B91" t="s">
+        <v>355</v>
+      </c>
+      <c r="C91" t="s">
+        <v>335</v>
+      </c>
+      <c r="D91" t="s">
+        <v>288</v>
+      </c>
+      <c r="E91" s="1">
+        <v>46055</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>395</v>
+      </c>
+      <c r="B92" t="s">
+        <v>396</v>
+      </c>
+      <c r="C92" t="s">
+        <v>335</v>
+      </c>
+      <c r="D92" t="s">
+        <v>288</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46134</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>397</v>
+      </c>
+      <c r="B93" t="s">
+        <v>398</v>
+      </c>
+      <c r="C93" t="s">
+        <v>335</v>
+      </c>
+      <c r="D93" t="s">
+        <v>288</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>244</v>
+      </c>
+      <c r="B94" t="s">
+        <v>356</v>
+      </c>
+      <c r="C94" t="s">
+        <v>335</v>
+      </c>
+      <c r="D94" t="s">
+        <v>268</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>246</v>
+      </c>
+      <c r="B95" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" t="s">
+        <v>335</v>
+      </c>
+      <c r="D95" t="s">
+        <v>281</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" t="s">
+        <v>358</v>
+      </c>
+      <c r="C96" t="s">
+        <v>335</v>
+      </c>
+      <c r="D96" t="s">
+        <v>328</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>250</v>
+      </c>
+      <c r="B97" t="s">
+        <v>359</v>
+      </c>
+      <c r="C97" t="s">
+        <v>335</v>
+      </c>
+      <c r="D97" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="F97" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>251</v>
+      </c>
+      <c r="B98" t="s">
+        <v>360</v>
+      </c>
+      <c r="C98" t="s">
+        <v>335</v>
+      </c>
+      <c r="D98" t="s">
+        <v>292</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>400</v>
+      </c>
+      <c r="B99" t="s">
+        <v>401</v>
+      </c>
+      <c r="C99" t="s">
+        <v>335</v>
+      </c>
+      <c r="D99" t="s">
+        <v>292</v>
+      </c>
+      <c r="E99" s="1">
+        <v>46072</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>403</v>
+      </c>
+      <c r="B100" t="s">
+        <v>402</v>
+      </c>
+      <c r="C100" t="s">
+        <v>335</v>
+      </c>
+      <c r="D100" t="s">
+        <v>292</v>
+      </c>
+      <c r="E100" s="1">
+        <v>46057</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>252</v>
+      </c>
+      <c r="B101" t="s">
+        <v>361</v>
+      </c>
+      <c r="C101" t="s">
+        <v>335</v>
+      </c>
+      <c r="D101" t="s">
+        <v>266</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>255</v>
+      </c>
+      <c r="B102" t="s">
+        <v>362</v>
+      </c>
+      <c r="C102" t="s">
+        <v>335</v>
+      </c>
+      <c r="D102" t="s">
+        <v>298</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>259</v>
+      </c>
+      <c r="B103" t="s">
+        <v>363</v>
+      </c>
+      <c r="C103" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103" t="s">
+        <v>292</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" t="s">
+        <v>364</v>
+      </c>
+      <c r="C104" t="s">
+        <v>335</v>
+      </c>
+      <c r="D104" t="s">
+        <v>298</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>46</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B105" t="s">
         <v>93</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C105" t="s">
         <v>144</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D105" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="F105" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>49</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B106" t="s">
         <v>79</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C106" t="s">
         <v>144</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D106" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="F106" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>59</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B107" t="s">
         <v>114</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C107" t="s">
         <v>144</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D107" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="F107" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>55</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B108" t="s">
         <v>121</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C108" t="s">
         <v>144</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D108" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="F108" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>4</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B109" t="s">
         <v>73</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C109" t="s">
         <v>144</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D109" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="F109" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>6</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B110" t="s">
         <v>133</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C110" t="s">
         <v>144</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D110" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="F110" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>5</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B111" t="s">
         <v>138</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C111" t="s">
         <v>144</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D111" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="F111" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>14</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B112" t="s">
         <v>74</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C112" t="s">
         <v>144</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D112" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="F112" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>53</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B113" t="s">
         <v>125</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C113" t="s">
         <v>144</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D113" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="F113" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>44</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B114" t="s">
         <v>96</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C114" t="s">
         <v>144</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D114" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="F114" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>52</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B115" t="s">
         <v>122</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C115" t="s">
         <v>144</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D115" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="F115" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>12</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B116" t="s">
         <v>137</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C116" t="s">
         <v>144</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D116" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+      <c r="F116" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B117" t="s">
         <v>374</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C117" t="s">
         <v>375</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D117" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="F117" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B118" t="s">
         <v>377</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C118" t="s">
         <v>375</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D118" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="F118" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B119" t="s">
         <v>387</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C119" t="s">
         <v>375</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D119" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="F119" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>50</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B120" t="s">
         <v>101</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C120" t="s">
         <v>142</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D120" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="F120" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>47</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B121" t="s">
         <v>80</v>
-      </c>
-      <c r="C103" t="s">
-        <v>142</v>
-      </c>
-      <c r="D103" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>48</v>
-      </c>
-      <c r="B104" t="s">
-        <v>113</v>
-      </c>
-      <c r="C104" t="s">
-        <v>142</v>
-      </c>
-      <c r="D104" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>60</v>
-      </c>
-      <c r="B105" t="s">
-        <v>134</v>
-      </c>
-      <c r="C105" t="s">
-        <v>142</v>
-      </c>
-      <c r="D105" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>379</v>
-      </c>
-      <c r="B106" t="s">
-        <v>380</v>
-      </c>
-      <c r="C106" t="s">
-        <v>381</v>
-      </c>
-      <c r="D106" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>39</v>
-      </c>
-      <c r="B107" t="s">
-        <v>69</v>
-      </c>
-      <c r="C107" t="s">
-        <v>142</v>
-      </c>
-      <c r="D107" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>40</v>
-      </c>
-      <c r="B108" t="s">
-        <v>123</v>
-      </c>
-      <c r="C108" t="s">
-        <v>142</v>
-      </c>
-      <c r="D108" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B109" t="s">
-        <v>85</v>
-      </c>
-      <c r="C109" t="s">
-        <v>142</v>
-      </c>
-      <c r="D109" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>21</v>
-      </c>
-      <c r="B110" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" t="s">
-        <v>142</v>
-      </c>
-      <c r="D110" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>30</v>
-      </c>
-      <c r="B111" t="s">
-        <v>116</v>
-      </c>
-      <c r="C111" t="s">
-        <v>142</v>
-      </c>
-      <c r="D111" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" t="s">
-        <v>89</v>
-      </c>
-      <c r="C112" t="s">
-        <v>142</v>
-      </c>
-      <c r="D112" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>51</v>
-      </c>
-      <c r="B113" t="s">
-        <v>126</v>
-      </c>
-      <c r="C113" t="s">
-        <v>142</v>
-      </c>
-      <c r="D113" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>37</v>
-      </c>
-      <c r="B114" t="s">
-        <v>78</v>
-      </c>
-      <c r="C114" t="s">
-        <v>142</v>
-      </c>
-      <c r="D114" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>38</v>
-      </c>
-      <c r="B115" t="s">
-        <v>120</v>
-      </c>
-      <c r="C115" t="s">
-        <v>142</v>
-      </c>
-      <c r="D115" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>36</v>
-      </c>
-      <c r="B116" t="s">
-        <v>130</v>
-      </c>
-      <c r="C116" t="s">
-        <v>142</v>
-      </c>
-      <c r="D116" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>13</v>
-      </c>
-      <c r="B117" t="s">
-        <v>90</v>
-      </c>
-      <c r="C117" t="s">
-        <v>142</v>
-      </c>
-      <c r="D117" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>28</v>
-      </c>
-      <c r="B118" t="s">
-        <v>117</v>
-      </c>
-      <c r="C118" t="s">
-        <v>142</v>
-      </c>
-      <c r="D118" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>27</v>
-      </c>
-      <c r="B119" t="s">
-        <v>91</v>
-      </c>
-      <c r="C119" t="s">
-        <v>142</v>
-      </c>
-      <c r="D119" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B120" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" t="s">
-        <v>381</v>
-      </c>
-      <c r="D120" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>8</v>
-      </c>
-      <c r="B121" t="s">
-        <v>92</v>
       </c>
       <c r="C121" t="s">
         <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C122" t="s">
         <v>142</v>
       </c>
       <c r="D122" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B123" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C123" t="s">
         <v>142</v>
       </c>
       <c r="D123" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>23</v>
+        <v>379</v>
       </c>
       <c r="B124" t="s">
-        <v>173</v>
+        <v>380</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>381</v>
       </c>
       <c r="D124" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B125" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C125" t="s">
         <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B126" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="C126" t="s">
         <v>142</v>
       </c>
       <c r="D126" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B127" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C127" t="s">
         <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C128" t="s">
         <v>142</v>
       </c>
       <c r="D128" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C129" t="s">
         <v>142</v>
       </c>
       <c r="D129" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="C130" t="s">
         <v>142</v>
       </c>
       <c r="D130" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s">
         <v>142</v>
       </c>
       <c r="D131" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>42</v>
+        <v>419</v>
       </c>
       <c r="B132" t="s">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="C132" t="s">
         <v>142</v>
       </c>
       <c r="D132" t="s">
+        <v>160</v>
+      </c>
+      <c r="E132" s="1">
+        <v>46118</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>37</v>
+      </c>
+      <c r="B133" t="s">
+        <v>78</v>
+      </c>
+      <c r="C133" t="s">
+        <v>142</v>
+      </c>
+      <c r="D133" t="s">
+        <v>168</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>38</v>
+      </c>
+      <c r="B134" t="s">
+        <v>120</v>
+      </c>
+      <c r="C134" t="s">
+        <v>142</v>
+      </c>
+      <c r="D134" t="s">
+        <v>168</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135" t="s">
+        <v>130</v>
+      </c>
+      <c r="C135" t="s">
+        <v>142</v>
+      </c>
+      <c r="D135" t="s">
+        <v>168</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+      <c r="B136" t="s">
+        <v>90</v>
+      </c>
+      <c r="C136" t="s">
+        <v>142</v>
+      </c>
+      <c r="D136" t="s">
+        <v>169</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" t="s">
+        <v>117</v>
+      </c>
+      <c r="C137" t="s">
+        <v>142</v>
+      </c>
+      <c r="D137" t="s">
+        <v>169</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>416</v>
+      </c>
+      <c r="B138" t="s">
+        <v>415</v>
+      </c>
+      <c r="C138" t="s">
+        <v>142</v>
+      </c>
+      <c r="D138" t="s">
+        <v>169</v>
+      </c>
+      <c r="E138" s="1">
+        <v>46129</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>27</v>
+      </c>
+      <c r="B139" t="s">
+        <v>91</v>
+      </c>
+      <c r="C139" t="s">
+        <v>142</v>
+      </c>
+      <c r="D139" t="s">
+        <v>169</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B140" t="s">
+        <v>384</v>
+      </c>
+      <c r="C140" t="s">
+        <v>381</v>
+      </c>
+      <c r="D140" t="s">
+        <v>385</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>92</v>
+      </c>
+      <c r="C141" t="s">
+        <v>142</v>
+      </c>
+      <c r="D141" t="s">
+        <v>170</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>124</v>
+      </c>
+      <c r="C142" t="s">
+        <v>142</v>
+      </c>
+      <c r="D142" t="s">
+        <v>170</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>43</v>
+      </c>
+      <c r="B143" t="s">
+        <v>94</v>
+      </c>
+      <c r="C143" t="s">
+        <v>142</v>
+      </c>
+      <c r="D143" t="s">
+        <v>170</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>23</v>
+      </c>
+      <c r="B144" t="s">
+        <v>173</v>
+      </c>
+      <c r="C144" t="s">
+        <v>142</v>
+      </c>
+      <c r="D144" t="s">
+        <v>172</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>35</v>
+      </c>
+      <c r="B145" t="s">
+        <v>87</v>
+      </c>
+      <c r="C145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D145" t="s">
+        <v>172</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>24</v>
+      </c>
+      <c r="B146" t="s">
+        <v>88</v>
+      </c>
+      <c r="C146" t="s">
+        <v>142</v>
+      </c>
+      <c r="D146" t="s">
+        <v>172</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147" t="s">
+        <v>98</v>
+      </c>
+      <c r="C147" t="s">
+        <v>142</v>
+      </c>
+      <c r="D147" t="s">
+        <v>174</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
+        <v>142</v>
+      </c>
+      <c r="D148" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="F148" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" t="s">
+        <v>115</v>
+      </c>
+      <c r="C149" t="s">
+        <v>142</v>
+      </c>
+      <c r="D149" t="s">
+        <v>175</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>17</v>
+      </c>
+      <c r="B150" t="s">
+        <v>129</v>
+      </c>
+      <c r="C150" t="s">
+        <v>142</v>
+      </c>
+      <c r="D150" t="s">
+        <v>175</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>411</v>
+      </c>
+      <c r="B151" t="s">
+        <v>412</v>
+      </c>
+      <c r="C151" t="s">
+        <v>142</v>
+      </c>
+      <c r="D151" t="s">
+        <v>175</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
+        <v>82</v>
+      </c>
+      <c r="C152" t="s">
+        <v>142</v>
+      </c>
+      <c r="D152" t="s">
+        <v>175</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>42</v>
+      </c>
+      <c r="B153" t="s">
+        <v>84</v>
+      </c>
+      <c r="C153" t="s">
+        <v>142</v>
+      </c>
+      <c r="D153" t="s">
+        <v>175</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>45</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B154" t="s">
         <v>100</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C154" t="s">
         <v>143</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D154" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="F154" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>54</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B155" t="s">
         <v>70</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C155" t="s">
         <v>143</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D155" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="F155" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>61</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B156" t="s">
         <v>72</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C156" t="s">
         <v>145</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D156" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="F156" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>58</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B157" t="s">
         <v>77</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C157" t="s">
         <v>145</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D157" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="F157" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>66</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B158" t="s">
         <v>95</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C158" t="s">
         <v>145</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D158" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="F158" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>41</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B159" t="s">
         <v>102</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C159" t="s">
         <v>145</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D159" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="F159" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>57</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B160" t="s">
         <v>110</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C160" t="s">
         <v>145</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D160" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="F160" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>3</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B161" t="s">
         <v>71</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C161" t="s">
         <v>146</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D161" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="F161" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>67</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B162" t="s">
         <v>128</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C162" t="s">
         <v>141</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D162" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="F162" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>1</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B163" t="s">
         <v>76</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C163" t="s">
         <v>141</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D163" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="F163" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>64</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B164" t="s">
         <v>111</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C164" t="s">
         <v>141</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D164" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="F164" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>0</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B165" t="s">
         <v>99</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C165" t="s">
         <v>141</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D165" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="F165" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>65</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B166" t="s">
         <v>112</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C166" t="s">
         <v>141</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D166" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+      <c r="F166" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>68</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B167" t="s">
         <v>119</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C167" t="s">
         <v>141</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D167" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+      <c r="F167" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>18</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B168" t="s">
         <v>131</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C168" t="s">
         <v>147</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D168" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="F168" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>19</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B169" t="s">
         <v>132</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C169" t="s">
         <v>147</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D169" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+      <c r="F169" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>15</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B170" t="s">
         <v>103</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C170" t="s">
         <v>147</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D170" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="F170" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>56</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B171" t="s">
         <v>127</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C171" t="s">
         <v>147</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D171" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="F171" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>29</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B172" t="s">
         <v>104</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C172" t="s">
         <v>148</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D172" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="F172" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>32</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B173" t="s">
         <v>105</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C173" t="s">
         <v>148</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D173" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+      <c r="F173" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>25</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B174" t="s">
         <v>106</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C174" t="s">
         <v>148</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D174" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+      <c r="F174" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>26</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B175" t="s">
         <v>107</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C175" t="s">
         <v>148</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D175" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="F175" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>33</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B176" t="s">
         <v>108</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C176" t="s">
         <v>148</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D176" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="F176" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>34</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B177" t="s">
         <v>109</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C177" t="s">
         <v>148</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D177" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="F177" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>367</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B178" t="s">
         <v>367</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C178" t="s">
         <v>148</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D178" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="F178" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>368</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B179" t="s">
         <v>368</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C179" t="s">
         <v>148</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D179" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="F179" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>369</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B180" t="s">
         <v>369</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C180" t="s">
         <v>148</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D180" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="F180" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>371</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B181" t="s">
         <v>371</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C181" t="s">
         <v>148</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D181" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B161" t="s">
+      <c r="F181" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B182" t="s">
         <v>149</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C182" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B162" t="s">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B183" t="s">
         <v>151</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C183" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B163" t="s">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B184" t="s">
         <v>152</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C184" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B164" t="s">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B185" t="s">
         <v>372</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C185" t="s">
         <v>150</v>
       </c>
     </row>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9A4681-50B8-4BE3-AEED-887107FFAE72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79598EF2-1155-45B2-AA64-9B916AB89F14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1215" windowWidth="20505" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="439">
   <si>
     <t>KRZ502593210</t>
   </si>
@@ -1353,10 +1353,6 @@
   </si>
   <si>
     <t>현대인베SB14호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20262-02-06</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2039,7 +2035,7 @@
         <v>266</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2056,7 +2052,7 @@
         <v>268</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2073,18 +2069,18 @@
         <v>268</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" t="s">
         <v>404</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>405</v>
-      </c>
-      <c r="C9" t="s">
-        <v>406</v>
       </c>
       <c r="D9" t="s">
         <v>268</v>
@@ -2093,18 +2089,18 @@
         <v>46078</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B10" t="s">
         <v>407</v>
       </c>
-      <c r="B10" t="s">
-        <v>408</v>
-      </c>
       <c r="C10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D10" t="s">
         <v>268</v>
@@ -2113,15 +2109,15 @@
         <v>46043</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" t="s">
         <v>409</v>
-      </c>
-      <c r="B11" t="s">
-        <v>410</v>
       </c>
       <c r="C11" t="s">
         <v>265</v>
@@ -2133,7 +2129,7 @@
         <v>46008</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2150,7 +2146,7 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2167,7 +2163,7 @@
         <v>266</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2184,7 +2180,7 @@
         <v>266</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2201,7 +2197,7 @@
         <v>273</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2218,15 +2214,15 @@
         <v>275</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>416</v>
+      </c>
+      <c r="B17" t="s">
         <v>417</v>
-      </c>
-      <c r="B17" t="s">
-        <v>418</v>
       </c>
       <c r="C17" t="s">
         <v>265</v>
@@ -2238,7 +2234,7 @@
         <v>46080</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2255,15 +2251,15 @@
         <v>277</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>430</v>
+      </c>
+      <c r="B19" t="s">
         <v>431</v>
-      </c>
-      <c r="B19" t="s">
-        <v>432</v>
       </c>
       <c r="C19" t="s">
         <v>265</v>
@@ -2275,7 +2271,7 @@
         <v>46128</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2292,7 +2288,7 @@
         <v>275</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2309,7 +2305,7 @@
         <v>279</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2326,7 +2322,7 @@
         <v>281</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2343,7 +2339,7 @@
         <v>281</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2360,7 +2356,7 @@
         <v>277</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2377,7 +2373,7 @@
         <v>277</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2394,7 +2390,7 @@
         <v>266</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2411,7 +2407,7 @@
         <v>266</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2428,7 +2424,7 @@
         <v>288</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2445,7 +2441,7 @@
         <v>290</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2462,7 +2458,7 @@
         <v>292</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2479,7 +2475,7 @@
         <v>292</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2496,7 +2492,7 @@
         <v>292</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2513,7 +2509,7 @@
         <v>296</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2530,7 +2526,7 @@
         <v>298</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2547,7 +2543,7 @@
         <v>298</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2564,7 +2560,7 @@
         <v>298</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2581,7 +2577,7 @@
         <v>288</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2598,7 +2594,7 @@
         <v>288</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2615,7 +2611,7 @@
         <v>288</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2632,7 +2628,7 @@
         <v>305</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2649,7 +2645,7 @@
         <v>290</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2666,7 +2662,7 @@
         <v>308</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2683,7 +2679,7 @@
         <v>268</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2700,7 +2696,7 @@
         <v>290</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2717,7 +2713,7 @@
         <v>275</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2734,7 +2730,7 @@
         <v>313</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2754,7 +2750,7 @@
         <v>46128</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2771,7 +2767,7 @@
         <v>268</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2788,7 +2784,7 @@
         <v>268</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2805,7 +2801,7 @@
         <v>317</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,7 +2818,7 @@
         <v>319</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2839,7 +2835,7 @@
         <v>305</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2856,7 +2852,7 @@
         <v>322</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2873,7 +2869,7 @@
         <v>296</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2890,7 +2886,7 @@
         <v>266</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2907,7 +2903,7 @@
         <v>266</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2924,7 +2920,7 @@
         <v>268</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2941,18 +2937,18 @@
         <v>328</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>432</v>
+      </c>
+      <c r="B59" t="s">
         <v>433</v>
       </c>
-      <c r="B59" t="s">
-        <v>434</v>
-      </c>
       <c r="C59" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D59" t="s">
         <v>328</v>
@@ -2961,27 +2957,27 @@
         <v>46100</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>434</v>
+      </c>
+      <c r="B60" t="s">
         <v>435</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>405</v>
+      </c>
+      <c r="D60" t="s">
         <v>436</v>
-      </c>
-      <c r="C60" t="s">
-        <v>406</v>
-      </c>
-      <c r="D60" t="s">
-        <v>437</v>
       </c>
       <c r="E60" s="1">
         <v>46064</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2998,7 +2994,7 @@
         <v>281</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -3015,7 +3011,7 @@
         <v>328</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -3032,15 +3028,15 @@
         <v>298</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>420</v>
+      </c>
+      <c r="B64" t="s">
         <v>421</v>
-      </c>
-      <c r="B64" t="s">
-        <v>422</v>
       </c>
       <c r="C64" t="s">
         <v>265</v>
@@ -3052,7 +3048,7 @@
         <v>46079</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -3069,7 +3065,7 @@
         <v>292</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -3086,7 +3082,7 @@
         <v>275</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -3103,7 +3099,7 @@
         <v>292</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3120,7 +3116,7 @@
         <v>288</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3137,7 +3133,7 @@
         <v>298</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -3154,15 +3150,15 @@
         <v>298</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>422</v>
+      </c>
+      <c r="B71" t="s">
         <v>423</v>
-      </c>
-      <c r="B71" t="s">
-        <v>424</v>
       </c>
       <c r="C71" t="s">
         <v>335</v>
@@ -3174,15 +3170,15 @@
         <v>46140</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>424</v>
+      </c>
+      <c r="B72" t="s">
         <v>425</v>
-      </c>
-      <c r="B72" t="s">
-        <v>426</v>
       </c>
       <c r="C72" t="s">
         <v>335</v>
@@ -3194,7 +3190,7 @@
         <v>46072</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3211,15 +3207,15 @@
         <v>308</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>412</v>
+      </c>
+      <c r="B74" t="s">
         <v>413</v>
-      </c>
-      <c r="B74" t="s">
-        <v>414</v>
       </c>
       <c r="C74" t="s">
         <v>335</v>
@@ -3231,7 +3227,7 @@
         <v>46078</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3248,7 +3244,7 @@
         <v>268</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3265,7 +3261,7 @@
         <v>292</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3282,7 +3278,7 @@
         <v>288</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3299,15 +3295,15 @@
         <v>277</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>426</v>
+      </c>
+      <c r="B79" t="s">
         <v>427</v>
-      </c>
-      <c r="B79" t="s">
-        <v>428</v>
       </c>
       <c r="C79" t="s">
         <v>335</v>
@@ -3319,15 +3315,15 @@
         <v>46078</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B80" t="s">
         <v>429</v>
-      </c>
-      <c r="B80" t="s">
-        <v>430</v>
       </c>
       <c r="C80" t="s">
         <v>335</v>
@@ -3339,7 +3335,7 @@
         <v>46072</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3356,7 +3352,7 @@
         <v>292</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3373,7 +3369,7 @@
         <v>298</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3390,7 +3386,7 @@
         <v>305</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3407,7 +3403,7 @@
         <v>308</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3424,7 +3420,7 @@
         <v>288</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3441,7 +3437,7 @@
         <v>328</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3458,7 +3454,7 @@
         <v>275</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3478,7 +3474,7 @@
         <v>45659</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3498,7 +3494,7 @@
         <v>45693</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3518,7 +3514,7 @@
         <v>45659</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3538,7 +3534,7 @@
         <v>46055</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3558,7 +3554,7 @@
         <v>46134</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3574,11 +3570,11 @@
       <c r="D93" t="s">
         <v>288</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>399</v>
+      <c r="E93" s="1">
+        <v>46059</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3595,7 +3591,7 @@
         <v>268</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3612,7 +3608,7 @@
         <v>281</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3629,7 +3625,7 @@
         <v>328</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3646,7 +3642,7 @@
         <v>298</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3663,15 +3659,15 @@
         <v>292</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>399</v>
+      </c>
+      <c r="B99" t="s">
         <v>400</v>
-      </c>
-      <c r="B99" t="s">
-        <v>401</v>
       </c>
       <c r="C99" t="s">
         <v>335</v>
@@ -3683,15 +3679,15 @@
         <v>46072</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B100" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C100" t="s">
         <v>335</v>
@@ -3703,7 +3699,7 @@
         <v>46057</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -3720,7 +3716,7 @@
         <v>266</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -3737,7 +3733,7 @@
         <v>298</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3754,7 +3750,7 @@
         <v>292</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3771,7 +3767,7 @@
         <v>298</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -4235,10 +4231,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>418</v>
+      </c>
+      <c r="B132" t="s">
         <v>419</v>
-      </c>
-      <c r="B132" t="s">
-        <v>420</v>
       </c>
       <c r="C132" t="s">
         <v>142</v>
@@ -4340,10 +4336,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B138" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C138" t="s">
         <v>142</v>
@@ -4564,10 +4560,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>410</v>
+      </c>
+      <c r="B151" t="s">
         <v>411</v>
-      </c>
-      <c r="B151" t="s">
-        <v>412</v>
       </c>
       <c r="C151" t="s">
         <v>142</v>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79598EF2-1155-45B2-AA64-9B916AB89F14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0B722B-E4B4-4764-A375-6820A0AE1428}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1215" windowWidth="20505" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="442">
   <si>
     <t>KRZ502593210</t>
   </si>
@@ -922,9 +922,6 @@
     <t>마이다스06호</t>
   </si>
   <si>
-    <t>채권형(원화)</t>
-  </si>
-  <si>
     <t>마이다스</t>
   </si>
   <si>
@@ -1126,15 +1123,9 @@
     <t>한화B1호</t>
   </si>
   <si>
-    <t xml:space="preserve">채권형(외화) </t>
-  </si>
-  <si>
     <t>브이아이SB21호</t>
   </si>
   <si>
-    <t>채권형(외화)</t>
-  </si>
-  <si>
     <t>한화110호</t>
   </si>
   <si>
@@ -1380,10 +1371,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>채권형(외화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">	KRZ502657400	</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1508,11 +1495,37 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>채권(원화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채권(외화)</t>
+    <t>채권형(원화/단독)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권(원화/단독)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권형(원화/수인)</t>
+  </si>
+  <si>
+    <t>채권(원화/수인)</t>
+  </si>
+  <si>
+    <t>채권형(외화/복합)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권(외화/복합)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">채권형(외화/복합) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권형(외화/SB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채권(외화/SB)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1558,18 +1571,23 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1594,8 +1612,8 @@
     <tableColumn id="2" xr3:uid="{F336053D-BD49-47F3-B249-5103E50F80C9}" name="Fund"/>
     <tableColumn id="3" xr3:uid="{E1C8362A-7D25-46CB-84F2-B24CBD02573D}" name="Group"/>
     <tableColumn id="4" xr3:uid="{BA29F747-744C-4972-9F74-DA724AD556E2}" name="Manager"/>
-    <tableColumn id="5" xr3:uid="{C22D9EDE-63FD-432F-8D76-ACB553928B79}" name="LaunchDate"/>
-    <tableColumn id="6" xr3:uid="{6C0805FC-F20A-4557-BD3F-24A9694B7E2C}" name="Team" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{C22D9EDE-63FD-432F-8D76-ACB553928B79}" name="LaunchDate" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{6C0805FC-F20A-4557-BD3F-24A9694B7E2C}" name="Team" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1928,9 +1946,10 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="12.375" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1944,13 +1963,13 @@
         <v>139</v>
       </c>
       <c r="D1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>389</v>
+        <v>362</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1966,8 +1985,8 @@
       <c r="D2" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>390</v>
+      <c r="F2" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1983,8 +2002,8 @@
       <c r="D3" t="s">
         <v>157</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>390</v>
+      <c r="F3" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2000,8 +2019,8 @@
       <c r="D4" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>390</v>
+      <c r="F4" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2017,8 +2036,8 @@
       <c r="D5" t="s">
         <v>182</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>390</v>
+      <c r="F5" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2029,13 +2048,13 @@
         <v>264</v>
       </c>
       <c r="C6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D6" t="s">
         <v>265</v>
       </c>
-      <c r="D6" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>437</v>
+      <c r="F6" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2043,16 +2062,16 @@
         <v>184</v>
       </c>
       <c r="B7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" t="s">
         <v>267</v>
       </c>
-      <c r="C7" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>437</v>
+      <c r="F7" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2060,76 +2079,76 @@
         <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>437</v>
+        <v>267</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C9" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E9" s="1">
+        <v>267</v>
+      </c>
+      <c r="E9" s="3">
         <v>46078</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>438</v>
+      <c r="F9" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B10" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C10" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
-      </c>
-      <c r="E10" s="1">
+        <v>267</v>
+      </c>
+      <c r="E10" s="3">
         <v>46043</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>438</v>
+      <c r="F10" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B11" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C11" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E11" s="1">
+        <v>267</v>
+      </c>
+      <c r="E11" s="3">
         <v>46008</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>437</v>
+      <c r="F11" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2137,16 +2156,16 @@
         <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s">
+        <v>435</v>
+      </c>
+      <c r="D12" t="s">
         <v>265</v>
       </c>
-      <c r="D12" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>437</v>
+      <c r="F12" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2154,16 +2173,16 @@
         <v>187</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C13" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" t="s">
         <v>265</v>
       </c>
-      <c r="D13" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>437</v>
+      <c r="F13" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2171,16 +2190,16 @@
         <v>188</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C14" t="s">
+        <v>435</v>
+      </c>
+      <c r="D14" t="s">
         <v>265</v>
       </c>
-      <c r="D14" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>437</v>
+      <c r="F14" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2188,16 +2207,16 @@
         <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>437</v>
+        <v>272</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2205,36 +2224,36 @@
         <v>190</v>
       </c>
       <c r="B16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" t="s">
         <v>274</v>
       </c>
-      <c r="C16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D16" t="s">
-        <v>275</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>437</v>
+      <c r="F16" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B17" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
-      </c>
-      <c r="E17" s="1">
+        <v>274</v>
+      </c>
+      <c r="E17" s="3">
         <v>46080</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>437</v>
+      <c r="F17" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2242,36 +2261,36 @@
         <v>191</v>
       </c>
       <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" t="s">
+        <v>435</v>
+      </c>
+      <c r="D18" t="s">
         <v>276</v>
       </c>
-      <c r="C18" t="s">
-        <v>265</v>
-      </c>
-      <c r="D18" t="s">
-        <v>277</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>437</v>
+      <c r="F18" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B19" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E19" s="1">
+        <v>276</v>
+      </c>
+      <c r="E19" s="3">
         <v>46128</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>437</v>
+      <c r="F19" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2279,16 +2298,16 @@
         <v>192</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C20" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>437</v>
+        <v>274</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2296,16 +2315,16 @@
         <v>193</v>
       </c>
       <c r="B21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>437</v>
+        <v>278</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2313,16 +2332,16 @@
         <v>194</v>
       </c>
       <c r="B22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" t="s">
         <v>280</v>
       </c>
-      <c r="C22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D22" t="s">
-        <v>281</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>437</v>
+      <c r="F22" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2330,16 +2349,16 @@
         <v>195</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>437</v>
+        <v>280</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2347,16 +2366,16 @@
         <v>196</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>437</v>
+        <v>276</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2364,16 +2383,16 @@
         <v>197</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
-        <v>277</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>437</v>
+        <v>276</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2381,16 +2400,16 @@
         <v>198</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
+        <v>435</v>
+      </c>
+      <c r="D26" t="s">
         <v>265</v>
       </c>
-      <c r="D26" t="s">
-        <v>266</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>437</v>
+      <c r="F26" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2398,16 +2417,16 @@
         <v>199</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
+        <v>435</v>
+      </c>
+      <c r="D27" t="s">
         <v>265</v>
       </c>
-      <c r="D27" t="s">
-        <v>266</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>437</v>
+      <c r="F27" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2415,16 +2434,16 @@
         <v>200</v>
       </c>
       <c r="B28" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" t="s">
+        <v>435</v>
+      </c>
+      <c r="D28" t="s">
         <v>287</v>
       </c>
-      <c r="C28" t="s">
-        <v>265</v>
-      </c>
-      <c r="D28" t="s">
-        <v>288</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>437</v>
+      <c r="F28" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2432,16 +2451,16 @@
         <v>201</v>
       </c>
       <c r="B29" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" t="s">
+        <v>435</v>
+      </c>
+      <c r="D29" t="s">
         <v>289</v>
       </c>
-      <c r="C29" t="s">
-        <v>265</v>
-      </c>
-      <c r="D29" t="s">
-        <v>290</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>437</v>
+      <c r="F29" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2449,16 +2468,16 @@
         <v>202</v>
       </c>
       <c r="B30" t="s">
+        <v>290</v>
+      </c>
+      <c r="C30" t="s">
+        <v>433</v>
+      </c>
+      <c r="D30" t="s">
         <v>291</v>
       </c>
-      <c r="C30" t="s">
-        <v>265</v>
-      </c>
-      <c r="D30" t="s">
-        <v>292</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>437</v>
+      <c r="F30" s="2" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2466,16 +2485,16 @@
         <v>203</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>437</v>
+        <v>291</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2483,16 +2502,16 @@
         <v>204</v>
       </c>
       <c r="B32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>437</v>
+        <v>291</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2500,16 +2519,16 @@
         <v>205</v>
       </c>
       <c r="B33" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" t="s">
         <v>295</v>
       </c>
-      <c r="C33" t="s">
-        <v>265</v>
-      </c>
-      <c r="D33" t="s">
-        <v>296</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>437</v>
+      <c r="F33" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,16 +2536,16 @@
         <v>206</v>
       </c>
       <c r="B34" t="s">
+        <v>296</v>
+      </c>
+      <c r="C34" t="s">
+        <v>435</v>
+      </c>
+      <c r="D34" t="s">
         <v>297</v>
       </c>
-      <c r="C34" t="s">
-        <v>265</v>
-      </c>
-      <c r="D34" t="s">
-        <v>298</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>437</v>
+      <c r="F34" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2534,16 +2553,16 @@
         <v>207</v>
       </c>
       <c r="B35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>437</v>
+        <v>297</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2551,16 +2570,16 @@
         <v>208</v>
       </c>
       <c r="B36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C36" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>437</v>
+        <v>297</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2568,16 +2587,16 @@
         <v>209</v>
       </c>
       <c r="B37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D37" t="s">
-        <v>288</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>437</v>
+        <v>287</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2585,16 +2604,16 @@
         <v>210</v>
       </c>
       <c r="B38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C38" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>437</v>
+        <v>287</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2602,16 +2621,16 @@
         <v>211</v>
       </c>
       <c r="B39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C39" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>437</v>
+        <v>287</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2619,16 +2638,16 @@
         <v>212</v>
       </c>
       <c r="B40" t="s">
+        <v>303</v>
+      </c>
+      <c r="C40" t="s">
+        <v>435</v>
+      </c>
+      <c r="D40" t="s">
         <v>304</v>
       </c>
-      <c r="C40" t="s">
-        <v>265</v>
-      </c>
-      <c r="D40" t="s">
-        <v>305</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>437</v>
+      <c r="F40" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2636,16 +2655,16 @@
         <v>213</v>
       </c>
       <c r="B41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C41" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D41" t="s">
-        <v>290</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>437</v>
+        <v>289</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2653,16 +2672,16 @@
         <v>214</v>
       </c>
       <c r="B42" t="s">
+        <v>306</v>
+      </c>
+      <c r="C42" t="s">
+        <v>435</v>
+      </c>
+      <c r="D42" t="s">
         <v>307</v>
       </c>
-      <c r="C42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D42" t="s">
-        <v>308</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>437</v>
+      <c r="F42" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2670,16 +2689,16 @@
         <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C43" t="s">
-        <v>265</v>
+        <v>433</v>
       </c>
       <c r="D43" t="s">
-        <v>268</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>437</v>
+        <v>267</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2687,16 +2706,16 @@
         <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C44" t="s">
-        <v>265</v>
+        <v>433</v>
       </c>
       <c r="D44" t="s">
-        <v>290</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>437</v>
+        <v>289</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2704,16 +2723,16 @@
         <v>232</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C45" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D45" t="s">
-        <v>275</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>437</v>
+        <v>274</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2721,36 +2740,36 @@
         <v>234</v>
       </c>
       <c r="B46" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" t="s">
+        <v>435</v>
+      </c>
+      <c r="D46" t="s">
         <v>312</v>
       </c>
-      <c r="C46" t="s">
-        <v>265</v>
-      </c>
-      <c r="D46" t="s">
-        <v>313</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>437</v>
+      <c r="F46" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C47" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D47" t="s">
-        <v>313</v>
-      </c>
-      <c r="E47" s="1">
+        <v>312</v>
+      </c>
+      <c r="E47" s="3">
         <v>46128</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>437</v>
+      <c r="F47" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2758,16 +2777,16 @@
         <v>238</v>
       </c>
       <c r="B48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>437</v>
+        <v>267</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2775,16 +2794,16 @@
         <v>240</v>
       </c>
       <c r="B49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D49" t="s">
-        <v>268</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>437</v>
+        <v>267</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2792,16 +2811,16 @@
         <v>242</v>
       </c>
       <c r="B50" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50" t="s">
+        <v>435</v>
+      </c>
+      <c r="D50" t="s">
         <v>316</v>
       </c>
-      <c r="C50" t="s">
-        <v>265</v>
-      </c>
-      <c r="D50" t="s">
-        <v>317</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>437</v>
+      <c r="F50" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2809,16 +2828,16 @@
         <v>245</v>
       </c>
       <c r="B51" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" t="s">
+        <v>435</v>
+      </c>
+      <c r="D51" t="s">
         <v>318</v>
       </c>
-      <c r="C51" t="s">
-        <v>265</v>
-      </c>
-      <c r="D51" t="s">
-        <v>319</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>437</v>
+      <c r="F51" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2826,16 +2845,16 @@
         <v>247</v>
       </c>
       <c r="B52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C52" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D52" t="s">
-        <v>305</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>437</v>
+        <v>304</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2843,16 +2862,16 @@
         <v>248</v>
       </c>
       <c r="B53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" t="s">
+        <v>435</v>
+      </c>
+      <c r="D53" t="s">
         <v>321</v>
       </c>
-      <c r="C53" t="s">
-        <v>265</v>
-      </c>
-      <c r="D53" t="s">
-        <v>322</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>437</v>
+      <c r="F53" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2860,16 +2879,16 @@
         <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D54" t="s">
-        <v>296</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>437</v>
+        <v>295</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2877,16 +2896,16 @@
         <v>254</v>
       </c>
       <c r="B55" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C55" t="s">
+        <v>435</v>
+      </c>
+      <c r="D55" t="s">
         <v>265</v>
       </c>
-      <c r="D55" t="s">
-        <v>266</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>437</v>
+      <c r="F55" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2894,16 +2913,16 @@
         <v>256</v>
       </c>
       <c r="B56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
+        <v>435</v>
+      </c>
+      <c r="D56" t="s">
         <v>265</v>
       </c>
-      <c r="D56" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>437</v>
+      <c r="F56" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2911,16 +2930,16 @@
         <v>257</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D57" t="s">
-        <v>268</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>437</v>
+        <v>267</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2928,56 +2947,56 @@
         <v>258</v>
       </c>
       <c r="B58" t="s">
+        <v>326</v>
+      </c>
+      <c r="C58" t="s">
+        <v>435</v>
+      </c>
+      <c r="D58" t="s">
         <v>327</v>
       </c>
-      <c r="C58" t="s">
-        <v>265</v>
-      </c>
-      <c r="D58" t="s">
-        <v>328</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>437</v>
+      <c r="F58" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C59" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="D59" t="s">
-        <v>328</v>
-      </c>
-      <c r="E59" s="1">
+        <v>327</v>
+      </c>
+      <c r="E59" s="3">
         <v>46100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>438</v>
+      <c r="F59" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C60" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="D60" t="s">
-        <v>436</v>
-      </c>
-      <c r="E60" s="1">
+        <v>432</v>
+      </c>
+      <c r="E60" s="3">
         <v>46064</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>438</v>
+      <c r="F60" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2985,16 +3004,16 @@
         <v>260</v>
       </c>
       <c r="B61" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C61" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D61" t="s">
-        <v>281</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>437</v>
+        <v>280</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -3002,16 +3021,16 @@
         <v>262</v>
       </c>
       <c r="B62" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C62" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D62" t="s">
-        <v>328</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>437</v>
+        <v>327</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -3019,36 +3038,36 @@
         <v>263</v>
       </c>
       <c r="B63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C63" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D63" t="s">
-        <v>298</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>437</v>
+        <v>297</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C64" t="s">
-        <v>265</v>
+        <v>435</v>
       </c>
       <c r="D64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E64" s="1">
+        <v>297</v>
+      </c>
+      <c r="E64" s="3">
         <v>46079</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>437</v>
+      <c r="F64" s="2" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -3056,15 +3075,15 @@
         <v>220</v>
       </c>
       <c r="B65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C65" t="s">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="D65" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>438</v>
       </c>
     </row>
@@ -3073,16 +3092,16 @@
         <v>217</v>
       </c>
       <c r="B66" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C66" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D66" t="s">
-        <v>275</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>438</v>
+        <v>274</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -3090,16 +3109,16 @@
         <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C67" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D67" t="s">
-        <v>292</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>438</v>
+        <v>291</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3107,16 +3126,16 @@
         <v>219</v>
       </c>
       <c r="B68" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C68" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D68" t="s">
-        <v>288</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>438</v>
+        <v>287</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3124,16 +3143,16 @@
         <v>221</v>
       </c>
       <c r="B69" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C69" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D69" t="s">
-        <v>298</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -3141,56 +3160,56 @@
         <v>222</v>
       </c>
       <c r="B70" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C70" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D70" t="s">
-        <v>298</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B71" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C71" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D71" t="s">
-        <v>298</v>
-      </c>
-      <c r="E71" s="1">
+        <v>297</v>
+      </c>
+      <c r="E71" s="3">
         <v>46140</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>438</v>
+      <c r="F71" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C72" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D72" t="s">
-        <v>298</v>
-      </c>
-      <c r="E72" s="1">
+        <v>297</v>
+      </c>
+      <c r="E72" s="3">
         <v>46072</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>438</v>
+      <c r="F72" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3198,36 +3217,36 @@
         <v>223</v>
       </c>
       <c r="B73" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C73" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D73" t="s">
-        <v>308</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>438</v>
+        <v>307</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B74" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C74" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D74" t="s">
-        <v>308</v>
-      </c>
-      <c r="E74" s="1">
+        <v>307</v>
+      </c>
+      <c r="E74" s="3">
         <v>46078</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>438</v>
+      <c r="F74" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3235,16 +3254,16 @@
         <v>224</v>
       </c>
       <c r="B75" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C75" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D75" t="s">
-        <v>268</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>438</v>
+        <v>267</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3252,16 +3271,16 @@
         <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C76" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D76" t="s">
-        <v>292</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>438</v>
+        <v>291</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3269,16 +3288,16 @@
         <v>226</v>
       </c>
       <c r="B77" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C77" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D77" t="s">
-        <v>288</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>438</v>
+        <v>287</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3286,56 +3305,56 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C78" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D78" t="s">
-        <v>277</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>438</v>
+        <v>276</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B79" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C79" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D79" t="s">
-        <v>277</v>
-      </c>
-      <c r="E79" s="1">
+        <v>276</v>
+      </c>
+      <c r="E79" s="3">
         <v>46078</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>438</v>
+      <c r="F79" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B80" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C80" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D80" t="s">
-        <v>277</v>
-      </c>
-      <c r="E80" s="1">
+        <v>276</v>
+      </c>
+      <c r="E80" s="3">
         <v>46072</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>438</v>
+      <c r="F80" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3343,16 +3362,16 @@
         <v>228</v>
       </c>
       <c r="B81" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C81" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D81" t="s">
-        <v>292</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>438</v>
+        <v>291</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3360,16 +3379,16 @@
         <v>229</v>
       </c>
       <c r="B82" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C82" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D82" t="s">
-        <v>298</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3377,16 +3396,16 @@
         <v>230</v>
       </c>
       <c r="B83" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C83" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D83" t="s">
-        <v>305</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>438</v>
+        <v>304</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3394,15 +3413,15 @@
         <v>231</v>
       </c>
       <c r="B84" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C84" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
-      </c>
-      <c r="F84" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>438</v>
       </c>
     </row>
@@ -3411,16 +3430,16 @@
         <v>233</v>
       </c>
       <c r="B85" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C85" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D85" t="s">
-        <v>288</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>438</v>
+        <v>287</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3428,16 +3447,16 @@
         <v>235</v>
       </c>
       <c r="B86" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C86" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D86" t="s">
-        <v>328</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>438</v>
+        <v>327</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3445,16 +3464,16 @@
         <v>236</v>
       </c>
       <c r="B87" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C87" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D87" t="s">
-        <v>275</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>438</v>
+        <v>274</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3462,19 +3481,19 @@
         <v>237</v>
       </c>
       <c r="B88" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C88" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D88" t="s">
-        <v>277</v>
-      </c>
-      <c r="E88" s="1">
+        <v>276</v>
+      </c>
+      <c r="E88" s="3">
         <v>45659</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>438</v>
+      <c r="F88" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3482,19 +3501,19 @@
         <v>239</v>
       </c>
       <c r="B89" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D89" t="s">
-        <v>288</v>
-      </c>
-      <c r="E89" s="1">
+        <v>287</v>
+      </c>
+      <c r="E89" s="3">
         <v>45693</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>438</v>
+      <c r="F89" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3502,18 +3521,18 @@
         <v>241</v>
       </c>
       <c r="B90" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C90" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>292</v>
-      </c>
-      <c r="E90" s="1">
+        <v>291</v>
+      </c>
+      <c r="E90" s="3">
         <v>45659</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>438</v>
       </c>
     </row>
@@ -3522,59 +3541,59 @@
         <v>243</v>
       </c>
       <c r="B91" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C91" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D91" t="s">
-        <v>288</v>
-      </c>
-      <c r="E91" s="1">
+        <v>287</v>
+      </c>
+      <c r="E91" s="3">
         <v>46055</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>438</v>
+      <c r="F91" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B92" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C92" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D92" t="s">
-        <v>288</v>
-      </c>
-      <c r="E92" s="1">
+        <v>287</v>
+      </c>
+      <c r="E92" s="3">
         <v>46134</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>438</v>
+      <c r="F92" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B93" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C93" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D93" t="s">
-        <v>288</v>
-      </c>
-      <c r="E93" s="1">
+        <v>287</v>
+      </c>
+      <c r="E93" s="3">
         <v>46059</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>438</v>
+      <c r="F93" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3582,16 +3601,16 @@
         <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C94" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>438</v>
+        <v>267</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3599,16 +3618,16 @@
         <v>246</v>
       </c>
       <c r="B95" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C95" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D95" t="s">
-        <v>281</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>438</v>
+        <v>280</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3616,16 +3635,16 @@
         <v>249</v>
       </c>
       <c r="B96" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C96" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D96" t="s">
-        <v>328</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>438</v>
+        <v>327</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3633,16 +3652,16 @@
         <v>250</v>
       </c>
       <c r="B97" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C97" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D97" t="s">
-        <v>298</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3650,56 +3669,56 @@
         <v>251</v>
       </c>
       <c r="B98" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C98" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
       <c r="D98" t="s">
-        <v>292</v>
-      </c>
-      <c r="F98" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B99" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D99" t="s">
-        <v>292</v>
-      </c>
-      <c r="E99" s="1">
+        <v>291</v>
+      </c>
+      <c r="E99" s="3">
         <v>46072</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>438</v>
+      <c r="F99" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B100" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D100" t="s">
-        <v>292</v>
-      </c>
-      <c r="E100" s="1">
+        <v>291</v>
+      </c>
+      <c r="E100" s="3">
         <v>46057</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>438</v>
+      <c r="F100" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -3707,16 +3726,16 @@
         <v>252</v>
       </c>
       <c r="B101" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D101" t="s">
-        <v>266</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>438</v>
+        <v>265</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -3724,16 +3743,16 @@
         <v>255</v>
       </c>
       <c r="B102" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C102" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D102" t="s">
-        <v>298</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3741,16 +3760,16 @@
         <v>259</v>
       </c>
       <c r="B103" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C103" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D103" t="s">
-        <v>292</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>438</v>
+        <v>291</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3758,16 +3777,16 @@
         <v>261</v>
       </c>
       <c r="B104" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C104" t="s">
-        <v>335</v>
+        <v>440</v>
       </c>
       <c r="D104" t="s">
-        <v>298</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>438</v>
+        <v>297</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3783,8 +3802,8 @@
       <c r="D105" t="s">
         <v>158</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>390</v>
+      <c r="F105" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -3800,8 +3819,8 @@
       <c r="D106" t="s">
         <v>160</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>390</v>
+      <c r="F106" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3817,8 +3836,8 @@
       <c r="D107" t="s">
         <v>160</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>390</v>
+      <c r="F107" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3834,8 +3853,8 @@
       <c r="D108" t="s">
         <v>162</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>390</v>
+      <c r="F108" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3851,8 +3870,8 @@
       <c r="D109" t="s">
         <v>163</v>
       </c>
-      <c r="F109" s="3" t="s">
-        <v>390</v>
+      <c r="F109" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3868,8 +3887,8 @@
       <c r="D110" t="s">
         <v>163</v>
       </c>
-      <c r="F110" s="3" t="s">
-        <v>390</v>
+      <c r="F110" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3885,8 +3904,8 @@
       <c r="D111" t="s">
         <v>163</v>
       </c>
-      <c r="F111" s="3" t="s">
-        <v>390</v>
+      <c r="F111" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -3902,8 +3921,8 @@
       <c r="D112" t="s">
         <v>164</v>
       </c>
-      <c r="F112" s="3" t="s">
-        <v>390</v>
+      <c r="F112" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3919,8 +3938,8 @@
       <c r="D113" t="s">
         <v>167</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>390</v>
+      <c r="F113" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3936,8 +3955,8 @@
       <c r="D114" t="s">
         <v>171</v>
       </c>
-      <c r="F114" s="3" t="s">
-        <v>390</v>
+      <c r="F114" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3953,8 +3972,8 @@
       <c r="D115" t="s">
         <v>171</v>
       </c>
-      <c r="F115" s="3" t="s">
-        <v>390</v>
+      <c r="F115" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -3970,59 +3989,59 @@
       <c r="D116" t="s">
         <v>180</v>
       </c>
-      <c r="F116" s="3" t="s">
-        <v>390</v>
+      <c r="F116" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B117" t="s">
+        <v>371</v>
+      </c>
+      <c r="C117" t="s">
+        <v>372</v>
+      </c>
+      <c r="D117" t="s">
+        <v>371</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B118" t="s">
         <v>374</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C118" t="s">
+        <v>372</v>
+      </c>
+      <c r="D118" t="s">
         <v>375</v>
       </c>
-      <c r="D117" t="s">
-        <v>374</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B118" t="s">
-        <v>377</v>
-      </c>
-      <c r="C118" t="s">
-        <v>375</v>
-      </c>
-      <c r="D118" t="s">
-        <v>378</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>390</v>
+      <c r="F118" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>386</v>
+      <c r="A119" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="B119" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" t="s">
+        <v>372</v>
+      </c>
+      <c r="D119" t="s">
+        <v>385</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="C119" t="s">
-        <v>375</v>
-      </c>
-      <c r="D119" t="s">
-        <v>388</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4038,8 +4057,8 @@
       <c r="D120" t="s">
         <v>154</v>
       </c>
-      <c r="F120" s="3" t="s">
-        <v>392</v>
+      <c r="F120" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4055,8 +4074,8 @@
       <c r="D121" t="s">
         <v>154</v>
       </c>
-      <c r="F121" s="3" t="s">
-        <v>392</v>
+      <c r="F121" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -4072,8 +4091,8 @@
       <c r="D122" t="s">
         <v>154</v>
       </c>
-      <c r="F122" s="3" t="s">
-        <v>392</v>
+      <c r="F122" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4089,25 +4108,25 @@
       <c r="D123" t="s">
         <v>154</v>
       </c>
-      <c r="F123" s="3" t="s">
-        <v>392</v>
+      <c r="F123" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>376</v>
+      </c>
+      <c r="B124" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" t="s">
+        <v>378</v>
+      </c>
+      <c r="D124" t="s">
         <v>379</v>
       </c>
-      <c r="B124" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" t="s">
-        <v>381</v>
-      </c>
-      <c r="D124" t="s">
-        <v>382</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>392</v>
+      <c r="F124" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4123,8 +4142,8 @@
       <c r="D125" t="s">
         <v>155</v>
       </c>
-      <c r="F125" s="3" t="s">
-        <v>392</v>
+      <c r="F125" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4140,8 +4159,8 @@
       <c r="D126" t="s">
         <v>155</v>
       </c>
-      <c r="F126" s="3" t="s">
-        <v>392</v>
+      <c r="F126" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -4157,8 +4176,8 @@
       <c r="D127" t="s">
         <v>159</v>
       </c>
-      <c r="F127" s="3" t="s">
-        <v>392</v>
+      <c r="F127" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -4174,8 +4193,8 @@
       <c r="D128" t="s">
         <v>159</v>
       </c>
-      <c r="F128" s="3" t="s">
-        <v>392</v>
+      <c r="F128" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4191,8 +4210,8 @@
       <c r="D129" t="s">
         <v>159</v>
       </c>
-      <c r="F129" s="3" t="s">
-        <v>392</v>
+      <c r="F129" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4208,8 +4227,8 @@
       <c r="D130" t="s">
         <v>159</v>
       </c>
-      <c r="F130" s="3" t="s">
-        <v>392</v>
+      <c r="F130" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4225,16 +4244,16 @@
       <c r="D131" t="s">
         <v>160</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>392</v>
+      <c r="F131" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B132" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C132" t="s">
         <v>142</v>
@@ -4242,11 +4261,11 @@
       <c r="D132" t="s">
         <v>160</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="3">
         <v>46118</v>
       </c>
-      <c r="F132" s="3" t="s">
-        <v>392</v>
+      <c r="F132" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -4262,8 +4281,8 @@
       <c r="D133" t="s">
         <v>168</v>
       </c>
-      <c r="F133" s="3" t="s">
-        <v>392</v>
+      <c r="F133" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -4279,8 +4298,8 @@
       <c r="D134" t="s">
         <v>168</v>
       </c>
-      <c r="F134" s="3" t="s">
-        <v>392</v>
+      <c r="F134" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
@@ -4296,8 +4315,8 @@
       <c r="D135" t="s">
         <v>168</v>
       </c>
-      <c r="F135" s="3" t="s">
-        <v>392</v>
+      <c r="F135" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -4313,8 +4332,8 @@
       <c r="D136" t="s">
         <v>169</v>
       </c>
-      <c r="F136" s="3" t="s">
-        <v>392</v>
+      <c r="F136" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -4330,16 +4349,16 @@
       <c r="D137" t="s">
         <v>169</v>
       </c>
-      <c r="F137" s="3" t="s">
-        <v>392</v>
+      <c r="F137" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B138" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C138" t="s">
         <v>142</v>
@@ -4347,11 +4366,11 @@
       <c r="D138" t="s">
         <v>169</v>
       </c>
-      <c r="E138" s="1">
+      <c r="E138" s="3">
         <v>46129</v>
       </c>
-      <c r="F138" s="3" t="s">
-        <v>392</v>
+      <c r="F138" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -4367,25 +4386,25 @@
       <c r="D139" t="s">
         <v>169</v>
       </c>
-      <c r="F139" s="3" t="s">
-        <v>392</v>
+      <c r="F139" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>383</v>
+      <c r="A140" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="B140" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C140" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -4401,8 +4420,8 @@
       <c r="D141" t="s">
         <v>170</v>
       </c>
-      <c r="F141" s="3" t="s">
-        <v>392</v>
+      <c r="F141" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -4418,8 +4437,8 @@
       <c r="D142" t="s">
         <v>170</v>
       </c>
-      <c r="F142" s="3" t="s">
-        <v>392</v>
+      <c r="F142" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -4435,8 +4454,8 @@
       <c r="D143" t="s">
         <v>170</v>
       </c>
-      <c r="F143" s="3" t="s">
-        <v>392</v>
+      <c r="F143" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -4452,8 +4471,8 @@
       <c r="D144" t="s">
         <v>172</v>
       </c>
-      <c r="F144" s="3" t="s">
-        <v>392</v>
+      <c r="F144" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -4469,8 +4488,8 @@
       <c r="D145" t="s">
         <v>172</v>
       </c>
-      <c r="F145" s="3" t="s">
-        <v>392</v>
+      <c r="F145" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -4486,8 +4505,8 @@
       <c r="D146" t="s">
         <v>172</v>
       </c>
-      <c r="F146" s="3" t="s">
-        <v>392</v>
+      <c r="F146" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -4503,8 +4522,8 @@
       <c r="D147" t="s">
         <v>174</v>
       </c>
-      <c r="F147" s="3" t="s">
-        <v>392</v>
+      <c r="F147" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -4520,8 +4539,8 @@
       <c r="D148" t="s">
         <v>175</v>
       </c>
-      <c r="F148" s="3" t="s">
-        <v>392</v>
+      <c r="F148" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -4537,8 +4556,8 @@
       <c r="D149" t="s">
         <v>175</v>
       </c>
-      <c r="F149" s="3" t="s">
-        <v>392</v>
+      <c r="F149" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -4554,16 +4573,16 @@
       <c r="D150" t="s">
         <v>175</v>
       </c>
-      <c r="F150" s="3" t="s">
-        <v>392</v>
+      <c r="F150" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B151" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C151" t="s">
         <v>142</v>
@@ -4571,8 +4590,8 @@
       <c r="D151" t="s">
         <v>175</v>
       </c>
-      <c r="F151" s="3" t="s">
-        <v>392</v>
+      <c r="F151" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -4588,8 +4607,8 @@
       <c r="D152" t="s">
         <v>175</v>
       </c>
-      <c r="F152" s="3" t="s">
-        <v>392</v>
+      <c r="F152" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -4605,8 +4624,8 @@
       <c r="D153" t="s">
         <v>175</v>
       </c>
-      <c r="F153" s="3" t="s">
-        <v>392</v>
+      <c r="F153" s="2" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -4622,8 +4641,8 @@
       <c r="D154" t="s">
         <v>154</v>
       </c>
-      <c r="F154" s="3" t="s">
-        <v>390</v>
+      <c r="F154" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -4639,8 +4658,8 @@
       <c r="D155" t="s">
         <v>156</v>
       </c>
-      <c r="F155" s="3" t="s">
-        <v>390</v>
+      <c r="F155" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -4656,8 +4675,8 @@
       <c r="D156" t="s">
         <v>161</v>
       </c>
-      <c r="F156" s="3" t="s">
-        <v>390</v>
+      <c r="F156" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -4673,8 +4692,8 @@
       <c r="D157" t="s">
         <v>166</v>
       </c>
-      <c r="F157" s="3" t="s">
-        <v>390</v>
+      <c r="F157" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -4690,8 +4709,8 @@
       <c r="D158" t="s">
         <v>171</v>
       </c>
-      <c r="F158" s="3" t="s">
-        <v>390</v>
+      <c r="F158" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -4707,8 +4726,8 @@
       <c r="D159" t="s">
         <v>179</v>
       </c>
-      <c r="F159" s="3" t="s">
-        <v>390</v>
+      <c r="F159" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -4724,8 +4743,8 @@
       <c r="D160" t="s">
         <v>179</v>
       </c>
-      <c r="F160" s="3" t="s">
-        <v>390</v>
+      <c r="F160" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -4741,8 +4760,8 @@
       <c r="D161" t="s">
         <v>146</v>
       </c>
-      <c r="F161" s="3" t="s">
-        <v>390</v>
+      <c r="F161" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -4758,8 +4777,8 @@
       <c r="D162" t="s">
         <v>153</v>
       </c>
-      <c r="F162" s="3" t="s">
-        <v>390</v>
+      <c r="F162" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -4775,8 +4794,8 @@
       <c r="D163" t="s">
         <v>165</v>
       </c>
-      <c r="F163" s="3" t="s">
-        <v>390</v>
+      <c r="F163" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -4792,8 +4811,8 @@
       <c r="D164" t="s">
         <v>176</v>
       </c>
-      <c r="F164" s="3" t="s">
-        <v>390</v>
+      <c r="F164" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -4809,8 +4828,8 @@
       <c r="D165" t="s">
         <v>176</v>
       </c>
-      <c r="F165" s="3" t="s">
-        <v>390</v>
+      <c r="F165" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -4826,8 +4845,8 @@
       <c r="D166" t="s">
         <v>177</v>
       </c>
-      <c r="F166" s="3" t="s">
-        <v>390</v>
+      <c r="F166" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -4843,8 +4862,8 @@
       <c r="D167" t="s">
         <v>178</v>
       </c>
-      <c r="F167" s="3" t="s">
-        <v>390</v>
+      <c r="F167" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
@@ -4860,8 +4879,8 @@
       <c r="D168" t="s">
         <v>180</v>
       </c>
-      <c r="F168" s="3" t="s">
-        <v>391</v>
+      <c r="F168" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -4877,8 +4896,8 @@
       <c r="D169" t="s">
         <v>180</v>
       </c>
-      <c r="F169" s="3" t="s">
-        <v>391</v>
+      <c r="F169" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -4894,8 +4913,8 @@
       <c r="D170" t="s">
         <v>180</v>
       </c>
-      <c r="F170" s="3" t="s">
-        <v>391</v>
+      <c r="F170" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -4911,8 +4930,8 @@
       <c r="D171" t="s">
         <v>180</v>
       </c>
-      <c r="F171" s="3" t="s">
-        <v>391</v>
+      <c r="F171" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -4928,8 +4947,8 @@
       <c r="D172" t="s">
         <v>181</v>
       </c>
-      <c r="F172" s="3" t="s">
-        <v>391</v>
+      <c r="F172" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
@@ -4945,8 +4964,8 @@
       <c r="D173" t="s">
         <v>181</v>
       </c>
-      <c r="F173" s="3" t="s">
-        <v>391</v>
+      <c r="F173" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -4962,8 +4981,8 @@
       <c r="D174" t="s">
         <v>181</v>
       </c>
-      <c r="F174" s="3" t="s">
-        <v>391</v>
+      <c r="F174" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -4979,8 +4998,8 @@
       <c r="D175" t="s">
         <v>181</v>
       </c>
-      <c r="F175" s="3" t="s">
-        <v>391</v>
+      <c r="F175" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -4996,8 +5015,8 @@
       <c r="D176" t="s">
         <v>181</v>
       </c>
-      <c r="F176" s="3" t="s">
-        <v>391</v>
+      <c r="F176" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -5013,76 +5032,76 @@
       <c r="D177" t="s">
         <v>181</v>
       </c>
-      <c r="F177" s="3" t="s">
-        <v>391</v>
+      <c r="F177" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C178" t="s">
         <v>148</v>
       </c>
       <c r="D178" t="s">
-        <v>370</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>391</v>
+        <v>367</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B179" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C179" t="s">
         <v>148</v>
       </c>
       <c r="D179" t="s">
-        <v>370</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>391</v>
+        <v>367</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B180" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C180" t="s">
         <v>148</v>
       </c>
       <c r="D180" t="s">
-        <v>370</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>391</v>
+        <v>367</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B181" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C181" t="s">
         <v>148</v>
       </c>
       <c r="D181" t="s">
-        <v>370</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>391</v>
+        <v>367</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -5111,7 +5130,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C185" t="s">
         <v>150</v>
